--- a/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCF95607-6D26-474F-84FC-D2D1D1D3A49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D6FDD8-DDC9-4349-AF85-D77762D63BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9E46B4BD-1601-49D7-B9BD-AC19D36AEE3F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E07EB243-2708-4A5A-9D5C-F9E65E7077CC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>e_w108020416-380</t>
   </si>
   <si>
-    <t>ep_bioenergy_w108020416-380__ember</t>
+    <t>ep_bioenergy_w108020416-380__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w109756016-380</t>
@@ -125,7 +125,7 @@
     <t>e_w109756016-380</t>
   </si>
   <si>
-    <t>ep_bioenergy_w109756016-380__ember</t>
+    <t>ep_bioenergy_w109756016-380__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w144005863-380</t>
@@ -134,28 +134,28 @@
     <t>e_w144005863-380</t>
   </si>
   <si>
-    <t>ep_bioenergy_w144005863-380__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w34157795-380__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w58440884-380__ember</t>
+    <t>ep_bioenergy_w144005863-380__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w34157795-380__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w58440884-380__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w81938081-380</t>
   </si>
   <si>
-    <t>ep_bioenergy_w81938081-380__ember</t>
+    <t>ep_bioenergy_w81938081-380__irena</t>
   </si>
   <si>
     <t>ep_bioenergy_w84696559-380</t>
   </si>
   <si>
-    <t>ep_bioenergy_w84696559-380__ember</t>
-  </si>
-  <si>
-    <t>ep_bioenergy_w98902899-380__ember</t>
+    <t>ep_bioenergy_w84696559-380__irena</t>
+  </si>
+  <si>
+    <t>ep_bioenergy_w98902899-380__irena</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000100198</t>
@@ -2069,28 +2069,28 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/108020416-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/109756016-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/144005863-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/34157795-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/58440884-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/81938081-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/84696559-380_Missing Bioenergy Capacity -- operating</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/98902899-380_Missing Bioenergy Capacity -- operating</t>
+    <t>Aggregated Plant - IRENA Gap - way/108020416-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/109756016-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/144005863-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/34157795-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/58440884-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/81938081-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/84696559-380_Missing Bioenergy Capacity -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - way/98902899-380_Missing Bioenergy Capacity -- operating</t>
   </si>
   <si>
     <t>Andrea Palladio power station_Unit 3 -- operating</t>
@@ -5113,7 +5113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E808A8C6-4F0B-4239-8D1D-6CFF0993E98F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9008ABB-441E-45BB-B004-97B96090A904}">
   <dimension ref="B9:T265"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19467,7 +19467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CE9139-D347-48FF-8004-7D653A80A2C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971B3B1A-B99F-4560-8936-77033631B6BC}">
   <dimension ref="B9:T101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24589,7 +24589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{525D0C1F-8947-4DD5-AC87-D4D5573673FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF382294-C945-46D8-81D5-9FE641B004CD}">
   <dimension ref="B9:T678"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24989,7 +24989,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>0.24877966101694915</v>
+        <v>0.19474701186440679</v>
       </c>
       <c r="G17">
         <v>0.37389000000000006</v>
@@ -25095,7 +25095,7 @@
         <v>2022</v>
       </c>
       <c r="F19">
-        <v>0.27911864406779663</v>
+        <v>0.21849664745762715</v>
       </c>
       <c r="G19">
         <v>0.37389000000000006</v>
@@ -25201,7 +25201,7 @@
         <v>2022</v>
       </c>
       <c r="F21">
-        <v>0.22450847457627116</v>
+        <v>0.17574730338983049</v>
       </c>
       <c r="G21">
         <v>0.37389000000000006</v>
@@ -25254,19 +25254,19 @@
         <v>2022</v>
       </c>
       <c r="F22">
-        <v>0.35800000000000004</v>
+        <v>0.28024569999999999</v>
       </c>
       <c r="G22">
-        <v>0.39655000000000001</v>
+        <v>0.37389000000000006</v>
       </c>
       <c r="H22">
-        <v>3850.0000000000009</v>
+        <v>4427.5</v>
       </c>
       <c r="I22">
-        <v>143</v>
+        <v>157.30000000000001</v>
       </c>
       <c r="J22">
-        <v>8.4</v>
+        <v>9.240000000000002</v>
       </c>
       <c r="K22">
         <v>50</v>
@@ -25307,7 +25307,7 @@
         <v>2022</v>
       </c>
       <c r="F23">
-        <v>0.51576271186440681</v>
+        <v>0.40374380508474578</v>
       </c>
       <c r="G23">
         <v>0.39655000000000001</v>
@@ -25413,7 +25413,7 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>0.49149152542372881</v>
+        <v>0.38474409661016951</v>
       </c>
       <c r="G25">
         <v>0.39655000000000001</v>
@@ -25519,13 +25519,13 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>1.0679322033898306</v>
+        <v>0.83598717288135593</v>
       </c>
       <c r="G27">
         <v>0.39655000000000001</v>
       </c>
       <c r="H27">
-        <v>3850.0000000000005</v>
+        <v>3850</v>
       </c>
       <c r="I27">
         <v>143</v>
@@ -25572,13 +25572,13 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>0.39440677966101695</v>
+        <v>0.30874526271186442</v>
       </c>
       <c r="G28">
         <v>0.39655000000000001</v>
       </c>
       <c r="H28">
-        <v>3850.0000000000005</v>
+        <v>3850.0000000000009</v>
       </c>
       <c r="I28">
         <v>143</v>
@@ -47089,7 +47089,7 @@
         <v>603</v>
       </c>
       <c r="P456" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q456" t="s">
         <v>666</v>
@@ -47142,7 +47142,7 @@
         <v>603</v>
       </c>
       <c r="P457" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q457" t="s">
         <v>666</v>
@@ -47354,7 +47354,7 @@
         <v>611</v>
       </c>
       <c r="P461" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q461" t="s">
         <v>666</v>
@@ -47407,7 +47407,7 @@
         <v>611</v>
       </c>
       <c r="P462" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q462" t="s">
         <v>666</v>
@@ -47460,7 +47460,7 @@
         <v>612</v>
       </c>
       <c r="P463" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q463" t="s">
         <v>666</v>
@@ -47513,7 +47513,7 @@
         <v>612</v>
       </c>
       <c r="P464" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q464" t="s">
         <v>666</v>
@@ -47551,7 +47551,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
       <c r="N465" t="s">
         <v>664</v>
@@ -47598,7 +47598,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
       <c r="N466" t="s">
         <v>664</v>
@@ -47645,7 +47645,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
       <c r="N467" t="s">
         <v>664</v>
@@ -48214,7 +48214,7 @@
         <v>638</v>
       </c>
       <c r="P477" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q477" t="s">
         <v>666</v>
@@ -48270,7 +48270,7 @@
         <v>638</v>
       </c>
       <c r="P478" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q478" t="s">
         <v>666</v>
@@ -48326,7 +48326,7 @@
         <v>640</v>
       </c>
       <c r="P479" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q479" t="s">
         <v>666</v>
@@ -48382,7 +48382,7 @@
         <v>640</v>
       </c>
       <c r="P480" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q480" t="s">
         <v>666</v>
@@ -50814,7 +50814,7 @@
         <v>33</v>
       </c>
       <c r="L544">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.45">
@@ -50840,7 +50840,7 @@
         <v>33</v>
       </c>
       <c r="L545">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="546" spans="2:12" x14ac:dyDescent="0.45">
@@ -50866,7 +50866,7 @@
         <v>33</v>
       </c>
       <c r="L546">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
     <row r="547" spans="2:12" x14ac:dyDescent="0.45">
@@ -55486,7 +55486,7 @@
         <v>50</v>
       </c>
       <c r="L678">
-        <v>0.17863101551144783</v>
+        <v>0.17863101551144786</v>
       </c>
     </row>
   </sheetData>
@@ -55495,7 +55495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E7A5160-D7A5-4A4D-9F21-DF84D323E8D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14BC46C-F2AE-4FB8-8285-A0A740FBEF8E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1D6FDD8-DDC9-4349-AF85-D77762D63BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3065B9A9-43EB-4F06-9F5B-C758B3B5C15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E07EB243-2708-4A5A-9D5C-F9E65E7077CC}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{0C023759-C021-49B5-94D4-3B93C4007D99}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -5113,7 +5113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9008ABB-441E-45BB-B004-97B96090A904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F87782C-DD2D-4C5A-B2F0-C4E4405C1C99}">
   <dimension ref="B9:T265"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19467,7 +19467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971B3B1A-B99F-4560-8936-77033631B6BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7259AA43-6379-44A6-B4DD-16A499B74236}">
   <dimension ref="B9:T101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24589,7 +24589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF382294-C945-46D8-81D5-9FE641B004CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1D12F0-F310-4BDB-8776-284C1F888E40}">
   <dimension ref="B9:T678"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -46506,7 +46506,7 @@
         <v>589</v>
       </c>
       <c r="P445" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q445" t="s">
         <v>666</v>
@@ -46559,7 +46559,7 @@
         <v>589</v>
       </c>
       <c r="P446" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q446" t="s">
         <v>666</v>
@@ -46718,7 +46718,7 @@
         <v>594</v>
       </c>
       <c r="P449" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q449" t="s">
         <v>666</v>
@@ -46771,7 +46771,7 @@
         <v>594</v>
       </c>
       <c r="P450" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q450" t="s">
         <v>666</v>
@@ -46983,7 +46983,7 @@
         <v>601</v>
       </c>
       <c r="P454" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q454" t="s">
         <v>666</v>
@@ -47036,7 +47036,7 @@
         <v>601</v>
       </c>
       <c r="P455" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q455" t="s">
         <v>666</v>
@@ -47089,7 +47089,7 @@
         <v>603</v>
       </c>
       <c r="P456" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q456" t="s">
         <v>666</v>
@@ -47142,7 +47142,7 @@
         <v>603</v>
       </c>
       <c r="P457" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q457" t="s">
         <v>666</v>
@@ -47354,7 +47354,7 @@
         <v>611</v>
       </c>
       <c r="P461" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q461" t="s">
         <v>666</v>
@@ -47407,7 +47407,7 @@
         <v>611</v>
       </c>
       <c r="P462" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q462" t="s">
         <v>666</v>
@@ -47551,7 +47551,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.20827624154866123</v>
+        <v>0.20827624154866117</v>
       </c>
       <c r="N465" t="s">
         <v>664</v>
@@ -47598,7 +47598,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.20827624154866123</v>
+        <v>0.20827624154866117</v>
       </c>
       <c r="N466" t="s">
         <v>664</v>
@@ -47645,7 +47645,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.20827624154866123</v>
+        <v>0.20827624154866117</v>
       </c>
       <c r="N467" t="s">
         <v>664</v>
@@ -48214,7 +48214,7 @@
         <v>638</v>
       </c>
       <c r="P477" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q477" t="s">
         <v>666</v>
@@ -48270,7 +48270,7 @@
         <v>638</v>
       </c>
       <c r="P478" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q478" t="s">
         <v>666</v>
@@ -48326,7 +48326,7 @@
         <v>640</v>
       </c>
       <c r="P479" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q479" t="s">
         <v>666</v>
@@ -48382,7 +48382,7 @@
         <v>640</v>
       </c>
       <c r="P480" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q480" t="s">
         <v>666</v>
@@ -55495,7 +55495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14BC46C-F2AE-4FB8-8285-A0A740FBEF8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA1A95D-A768-4FB1-A30B-BEF697E8CE42}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3065B9A9-43EB-4F06-9F5B-C758B3B5C15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E711ABE-9F9E-4F26-B0D9-ADACC2EFCD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" xr2:uid="{0C023759-C021-49B5-94D4-3B93C4007D99}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{332CC30C-F216-4F37-96BD-5BCC8E1D129A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -5113,7 +5113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F87782C-DD2D-4C5A-B2F0-C4E4405C1C99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF43AEF5-3C64-43EF-919D-9DBB38BBF3BF}">
   <dimension ref="B9:T265"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19467,7 +19467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7259AA43-6379-44A6-B4DD-16A499B74236}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C5AA5A-AE3A-4054-8FEE-5FB7E1CA733C}">
   <dimension ref="B9:T101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24589,7 +24589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C1D12F0-F310-4BDB-8776-284C1F888E40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93190A35-A003-4343-BFC0-0E67D3E2ED8D}">
   <dimension ref="B9:T678"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47089,7 +47089,7 @@
         <v>603</v>
       </c>
       <c r="P456" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q456" t="s">
         <v>666</v>
@@ -47142,7 +47142,7 @@
         <v>603</v>
       </c>
       <c r="P457" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q457" t="s">
         <v>666</v>
@@ -47460,7 +47460,7 @@
         <v>612</v>
       </c>
       <c r="P463" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q463" t="s">
         <v>666</v>
@@ -47513,7 +47513,7 @@
         <v>612</v>
       </c>
       <c r="P464" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q464" t="s">
         <v>666</v>
@@ -47551,7 +47551,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866115</v>
       </c>
       <c r="N465" t="s">
         <v>664</v>
@@ -47598,7 +47598,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866115</v>
       </c>
       <c r="N466" t="s">
         <v>664</v>
@@ -47645,7 +47645,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866115</v>
       </c>
       <c r="N467" t="s">
         <v>664</v>
@@ -48214,7 +48214,7 @@
         <v>638</v>
       </c>
       <c r="P477" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q477" t="s">
         <v>666</v>
@@ -48270,7 +48270,7 @@
         <v>638</v>
       </c>
       <c r="P478" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q478" t="s">
         <v>666</v>
@@ -48326,7 +48326,7 @@
         <v>640</v>
       </c>
       <c r="P479" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q479" t="s">
         <v>666</v>
@@ -48382,7 +48382,7 @@
         <v>640</v>
       </c>
       <c r="P480" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q480" t="s">
         <v>666</v>
@@ -50814,7 +50814,7 @@
         <v>33</v>
       </c>
       <c r="L544">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="545" spans="2:12" x14ac:dyDescent="0.45">
@@ -50840,7 +50840,7 @@
         <v>33</v>
       </c>
       <c r="L545">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="546" spans="2:12" x14ac:dyDescent="0.45">
@@ -50866,7 +50866,7 @@
         <v>33</v>
       </c>
       <c r="L546">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
     <row r="547" spans="2:12" x14ac:dyDescent="0.45">
@@ -55486,7 +55486,7 @@
         <v>50</v>
       </c>
       <c r="L678">
-        <v>0.17863101551144786</v>
+        <v>0.17863101551144783</v>
       </c>
     </row>
   </sheetData>
@@ -55495,7 +55495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA1A95D-A768-4FB1-A30B-BEF697E8CE42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906A281A-DD82-4658-804A-D2F76D6D3C05}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA_grids_kan/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E711ABE-9F9E-4F26-B0D9-ADACC2EFCD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7EE9ECD-F47B-4C3B-A250-B99C4D4E5DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{332CC30C-F216-4F37-96BD-5BCC8E1D129A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F1271EAC-DEC3-4C9C-9409-DDF6AF86BA49}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -5113,7 +5113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF43AEF5-3C64-43EF-919D-9DBB38BBF3BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A8E42A-9FE3-465D-89F6-83E2FE851392}">
   <dimension ref="B9:T265"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19467,7 +19467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5C5AA5A-AE3A-4054-8FEE-5FB7E1CA733C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B25745-614C-464A-885D-13EC6D1FD685}">
   <dimension ref="B9:T101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24589,7 +24589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93190A35-A003-4343-BFC0-0E67D3E2ED8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E45B512-C331-4E58-BD29-1406FC2714A0}">
   <dimension ref="B9:T678"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -47354,7 +47354,7 @@
         <v>611</v>
       </c>
       <c r="P461" t="s">
-        <v>674</v>
+        <v>791</v>
       </c>
       <c r="Q461" t="s">
         <v>666</v>
@@ -47407,7 +47407,7 @@
         <v>611</v>
       </c>
       <c r="P462" t="s">
-        <v>791</v>
+        <v>674</v>
       </c>
       <c r="Q462" t="s">
         <v>666</v>
@@ -55495,7 +55495,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906A281A-DD82-4658-804A-D2F76D6D3C05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E02B66-9D85-4926-8515-D772EBD759DE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
